--- a/daikibo-equality-table-completed.xlsx
+++ b/daikibo-equality-table-completed.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/faribakazi/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{200358E6-3646-964F-AD68-0DD8AE577C5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E19F4D1-E29E-164F-B57A-2BC4910653BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="daikibo-equality-table" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -133,8 +133,98 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFC6EFCE"/>
+      <rgbColor rgb="FFFFEB9C"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFC7CE"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -147,17 +237,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{56C110FD-7E9B-5643-B1BC-A4E4B6F8BF8A}" name="Table1" displayName="Table1" ref="A1:D38" totalsRowShown="0">
-  <autoFilter ref="A1:D38" xr:uid="{56C110FD-7E9B-5643-B1BC-A4E4B6F8BF8A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:D38" totalsRowShown="0">
+  <autoFilter ref="A1:D38" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{90B5BF95-FFE9-214F-86E5-51209E84E7A6}" name="Factory"/>
-    <tableColumn id="2" xr3:uid="{03305927-A381-EC42-95F5-8BE6AF6C296E}" name="Job Role"/>
-    <tableColumn id="3" xr3:uid="{D3CD8A1C-4F21-5A43-9B8E-D70BCEA0F20B}" name="Equality Score"/>
-    <tableColumn id="4" xr3:uid="{69C158E3-99D6-5B4E-B197-40FCD9523ABE}" name="Equality class">
-      <calculatedColumnFormula>IF(ABS(C2)&lt;=10,"Fair",IF(ABS(C2)&lt;=20,"Unfair","Highly Discriminative"))</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Factory"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Job Role"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Equality Score"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Equality class"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -919,6 +1007,17 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D2:D38">
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>$D2="Fair"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="3">
+      <formula>$D2="Unfair"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>$D2="Highly Discriminative"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
